--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-urinalysis</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-urinalysis</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4824" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4824" uniqueCount="544">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3861,7 +3853,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3879,23 +3871,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3922,10 +3914,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3933,13 +3925,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -3983,7 +3975,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -4001,10 +3993,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -4046,10 +4038,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4057,14 +4049,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4086,16 +4078,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4105,29 +4097,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4144,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4159,30 +4151,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4205,19 +4197,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4266,7 +4258,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4281,19 +4273,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4301,10 +4293,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4327,16 +4319,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4386,7 +4378,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4407,13 +4399,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4421,14 +4413,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4447,19 +4439,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4508,7 +4500,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4523,19 +4515,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4543,14 +4535,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4569,19 +4561,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4630,7 +4622,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4645,19 +4637,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4665,10 +4657,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4691,16 +4683,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4750,7 +4742,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4771,13 +4763,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4785,10 +4777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4811,17 +4803,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4870,7 +4862,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4885,19 +4877,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4905,10 +4897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4931,19 +4923,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4992,7 +4984,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5001,7 +4993,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5010,27 +5002,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5056,16 +5048,16 @@
         <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -5090,14 +5082,14 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
       </c>
@@ -5114,7 +5106,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5123,7 +5115,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -5138,7 +5130,7 @@
         <v>133</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -5149,14 +5141,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5178,16 +5170,16 @@
         <v>188</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -5212,14 +5204,14 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
@@ -5236,7 +5228,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5254,27 +5246,27 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5297,19 +5289,19 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5358,7 +5350,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5379,10 +5371,10 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5393,10 +5385,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5422,13 +5414,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5454,14 +5446,14 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5478,7 +5470,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5496,27 +5488,27 @@
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5542,16 +5534,16 @@
         <v>188</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5576,14 +5568,14 @@
         <v>18</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5600,7 +5592,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5621,10 +5613,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5635,10 +5627,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5661,16 +5653,16 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5720,7 +5712,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5738,27 +5730,27 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5781,16 +5773,16 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5840,7 +5832,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5858,27 +5850,27 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5901,19 +5893,19 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5962,7 +5954,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5974,19 +5966,19 @@
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -5997,10 +5989,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6023,13 +6015,13 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6080,7 +6072,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6104,7 +6096,7 @@
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -6115,10 +6107,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6147,7 +6139,7 @@
         <v>137</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -6200,7 +6192,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6224,7 +6216,7 @@
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6235,14 +6227,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6264,10 +6256,10 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>139</v>
@@ -6322,7 +6314,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6357,10 +6349,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6383,13 +6375,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6440,7 +6432,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6449,7 +6441,7 @@
         <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
@@ -6461,10 +6453,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6475,10 +6467,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6501,13 +6493,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6558,7 +6550,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6567,7 +6559,7 @@
         <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>102</v>
@@ -6579,10 +6571,10 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6593,10 +6585,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6622,16 +6614,16 @@
         <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6659,11 +6651,11 @@
         <v>114</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6680,7 +6672,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6698,13 +6690,13 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>18</v>
@@ -6715,10 +6707,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6744,16 +6736,16 @@
         <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6778,14 +6770,14 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
       </c>
@@ -6802,7 +6794,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6820,13 +6812,13 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6837,10 +6829,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6863,17 +6855,17 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6922,7 +6914,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6946,7 +6938,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -6957,10 +6949,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6983,13 +6975,13 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7040,7 +7032,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7061,10 +7053,10 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7075,10 +7067,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7101,16 +7093,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7160,7 +7152,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7181,10 +7173,10 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -7195,10 +7187,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7221,16 +7213,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7280,7 +7272,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7301,10 +7293,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7315,10 +7307,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7341,19 +7333,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7390,17 +7382,17 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7421,10 +7413,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7435,10 +7427,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7461,13 +7453,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7518,7 +7510,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7542,7 +7534,7 @@
         <v>18</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7553,10 +7545,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7585,7 +7577,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7638,7 +7630,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7662,7 +7654,7 @@
         <v>18</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7673,14 +7665,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7702,10 +7694,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7760,7 +7752,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7795,10 +7787,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7824,16 +7816,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7858,14 +7850,14 @@
         <v>18</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7882,7 +7874,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7900,16 +7892,16 @@
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>18</v>
@@ -7917,10 +7909,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7943,19 +7935,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -8004,7 +7996,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8022,27 +8014,27 @@
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8068,16 +8060,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -8102,14 +8094,14 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8126,7 +8118,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8135,7 +8127,7 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -8150,7 +8142,7 @@
         <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8161,14 +8153,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8190,16 +8182,16 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8224,14 +8216,14 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
       </c>
@@ -8248,7 +8240,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8266,27 +8258,27 @@
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8312,16 +8304,16 @@
         <v>80</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8370,7 +8362,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8391,10 +8383,10 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8405,13 +8397,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>18</v>
@@ -8433,19 +8425,19 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8494,7 +8486,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8515,10 +8507,10 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8529,10 +8521,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8555,13 +8547,13 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8612,7 +8604,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8636,7 +8628,7 @@
         <v>18</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
@@ -8647,10 +8639,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8679,7 +8671,7 @@
         <v>137</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8732,7 +8724,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8756,7 +8748,7 @@
         <v>18</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
@@ -8767,14 +8759,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8796,10 +8788,10 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>139</v>
@@ -8854,7 +8846,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8889,10 +8881,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8918,16 +8910,16 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8937,7 +8929,7 @@
         <v>18</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>18</v>
@@ -8952,14 +8944,14 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8976,7 +8968,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>90</v>
@@ -8994,16 +8986,16 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>18</v>
@@ -9011,10 +9003,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9037,19 +9029,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9098,7 +9090,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9116,27 +9108,27 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9162,16 +9154,16 @@
         <v>188</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9196,14 +9188,14 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>18</v>
       </c>
@@ -9220,7 +9212,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9229,7 +9221,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -9244,7 +9236,7 @@
         <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9255,14 +9247,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9284,16 +9276,16 @@
         <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9318,14 +9310,14 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9342,7 +9334,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9360,27 +9352,27 @@
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9406,16 +9398,16 @@
         <v>80</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N61" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>18</v>
@@ -9464,7 +9456,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9485,10 +9477,10 @@
         <v>18</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9499,13 +9491,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>18</v>
@@ -9527,19 +9519,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>18</v>
@@ -9588,7 +9580,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9609,10 +9601,10 @@
         <v>18</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9623,10 +9615,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9649,13 +9641,13 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9706,7 +9698,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9730,7 +9722,7 @@
         <v>18</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
@@ -9741,10 +9733,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9773,7 +9765,7 @@
         <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>139</v>
@@ -9826,7 +9818,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9850,7 +9842,7 @@
         <v>18</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>18</v>
@@ -9861,14 +9853,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9890,10 +9882,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>139</v>
@@ -9948,7 +9940,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9983,10 +9975,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10012,16 +10004,16 @@
         <v>188</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N66" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O66" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -10031,7 +10023,7 @@
         <v>18</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>18</v>
@@ -10046,14 +10038,14 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y66" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Z66" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
       </c>
@@ -10070,7 +10062,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>90</v>
@@ -10088,16 +10080,16 @@
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>18</v>
@@ -10105,10 +10097,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10131,19 +10123,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10192,7 +10184,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10210,27 +10202,27 @@
         <v>18</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10256,16 +10248,16 @@
         <v>188</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O68" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -10290,14 +10282,14 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y68" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y68" t="s" s="2">
+      <c r="Z68" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
       </c>
@@ -10314,7 +10306,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10323,7 +10315,7 @@
         <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>102</v>
@@ -10338,7 +10330,7 @@
         <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>18</v>
@@ -10349,14 +10341,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10378,16 +10370,16 @@
         <v>188</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -10412,14 +10404,14 @@
         <v>18</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>18</v>
       </c>
@@ -10436,7 +10428,7 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10454,27 +10446,27 @@
         <v>18</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10500,16 +10492,16 @@
         <v>80</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N70" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -10558,7 +10550,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10579,10 +10571,10 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10593,13 +10585,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>18</v>
@@ -10621,19 +10613,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>18</v>
@@ -10682,7 +10674,7 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10703,10 +10695,10 @@
         <v>18</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10717,10 +10709,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10743,13 +10735,13 @@
         <v>18</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10800,7 +10792,7 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10824,7 +10816,7 @@
         <v>18</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>18</v>
@@ -10835,10 +10827,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10867,7 +10859,7 @@
         <v>137</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>139</v>
@@ -10920,7 +10912,7 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10944,7 +10936,7 @@
         <v>18</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>18</v>
@@ -10955,14 +10947,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10984,10 +10976,10 @@
         <v>136</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>139</v>
@@ -11042,7 +11034,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11077,10 +11069,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11106,16 +11098,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -11125,7 +11117,7 @@
         <v>18</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>18</v>
@@ -11140,14 +11132,14 @@
         <v>18</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y75" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Z75" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>18</v>
       </c>
@@ -11164,7 +11156,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -11182,16 +11174,16 @@
         <v>18</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>18</v>
@@ -11199,10 +11191,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11225,19 +11217,19 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -11286,7 +11278,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11304,27 +11296,27 @@
         <v>18</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11350,16 +11342,16 @@
         <v>188</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O77" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
@@ -11384,14 +11376,14 @@
         <v>18</v>
       </c>
       <c r="X77" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y77" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y77" t="s" s="2">
+      <c r="Z77" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>18</v>
       </c>
@@ -11408,7 +11400,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11417,7 +11409,7 @@
         <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
@@ -11432,7 +11424,7 @@
         <v>133</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
@@ -11443,14 +11435,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11472,16 +11464,16 @@
         <v>188</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>18</v>
@@ -11506,14 +11498,14 @@
         <v>18</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>18</v>
       </c>
@@ -11530,7 +11522,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11548,27 +11540,27 @@
         <v>18</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11594,16 +11586,16 @@
         <v>80</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N79" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O79" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>18</v>
@@ -11652,7 +11644,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11673,10 +11665,10 @@
         <v>18</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11687,13 +11679,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C80" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>18</v>
@@ -11715,19 +11707,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>18</v>
@@ -11776,7 +11768,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11797,10 +11789,10 @@
         <v>18</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>18</v>
@@ -11811,10 +11803,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11837,13 +11829,13 @@
         <v>18</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11894,7 +11886,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11918,7 +11910,7 @@
         <v>18</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>18</v>
@@ -11929,10 +11921,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11961,7 +11953,7 @@
         <v>137</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>139</v>
@@ -12014,7 +12006,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12038,7 +12030,7 @@
         <v>18</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>18</v>
@@ -12049,14 +12041,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12078,10 +12070,10 @@
         <v>136</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>139</v>
@@ -12136,7 +12128,7 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12171,10 +12163,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12200,16 +12192,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12219,7 +12211,7 @@
         <v>18</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>18</v>
@@ -12234,14 +12226,14 @@
         <v>18</v>
       </c>
       <c r="X84" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y84" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Z84" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>18</v>
       </c>
@@ -12258,7 +12250,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>90</v>
@@ -12276,16 +12268,16 @@
         <v>18</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>18</v>
@@ -12293,10 +12285,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12319,19 +12311,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O85" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>18</v>
@@ -12380,7 +12372,7 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12398,27 +12390,27 @@
         <v>18</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12444,16 +12436,16 @@
         <v>188</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N86" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O86" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -12478,14 +12470,14 @@
         <v>18</v>
       </c>
       <c r="X86" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y86" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y86" t="s" s="2">
+      <c r="Z86" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>18</v>
       </c>
@@ -12502,7 +12494,7 @@
         <v>18</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12511,7 +12503,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -12526,7 +12518,7 @@
         <v>133</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>18</v>
@@ -12537,14 +12529,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12566,16 +12558,16 @@
         <v>188</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>18</v>
@@ -12600,14 +12592,14 @@
         <v>18</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>18</v>
       </c>
@@ -12624,7 +12616,7 @@
         <v>18</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12642,27 +12634,27 @@
         <v>18</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AN87" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12688,16 +12680,16 @@
         <v>80</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N88" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O88" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>18</v>
@@ -12746,7 +12738,7 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12767,10 +12759,10 @@
         <v>18</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>18</v>
@@ -12781,13 +12773,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C89" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>18</v>
@@ -12809,19 +12801,19 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>18</v>
@@ -12870,7 +12862,7 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12891,10 +12883,10 @@
         <v>18</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>18</v>
@@ -12905,10 +12897,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12931,13 +12923,13 @@
         <v>18</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12988,7 +12980,7 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13012,7 +13004,7 @@
         <v>18</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>18</v>
@@ -13023,10 +13015,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13055,7 +13047,7 @@
         <v>137</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>139</v>
@@ -13108,7 +13100,7 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13132,7 +13124,7 @@
         <v>18</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>18</v>
@@ -13143,14 +13135,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13172,10 +13164,10 @@
         <v>136</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>139</v>
@@ -13230,7 +13222,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13265,10 +13257,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13294,16 +13286,16 @@
         <v>188</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N93" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>18</v>
@@ -13313,7 +13305,7 @@
         <v>18</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>18</v>
@@ -13328,14 +13320,14 @@
         <v>18</v>
       </c>
       <c r="X93" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y93" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y93" t="s" s="2">
+      <c r="Z93" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>18</v>
       </c>
@@ -13352,7 +13344,7 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>90</v>
@@ -13370,16 +13362,16 @@
         <v>18</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>18</v>
@@ -13387,10 +13379,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13413,19 +13405,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M94" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O94" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>18</v>
@@ -13474,7 +13466,7 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13492,27 +13484,27 @@
         <v>18</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13538,16 +13530,16 @@
         <v>188</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>18</v>
@@ -13572,14 +13564,14 @@
         <v>18</v>
       </c>
       <c r="X95" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y95" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y95" t="s" s="2">
+      <c r="Z95" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>18</v>
       </c>
@@ -13596,7 +13588,7 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13605,7 +13597,7 @@
         <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>102</v>
@@ -13620,7 +13612,7 @@
         <v>133</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>18</v>
@@ -13631,14 +13623,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13660,16 +13652,16 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>18</v>
@@ -13694,14 +13686,14 @@
         <v>18</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z96" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA96" t="s" s="2">
         <v>18</v>
       </c>
@@ -13718,7 +13710,7 @@
         <v>18</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13736,27 +13728,27 @@
         <v>18</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13782,16 +13774,16 @@
         <v>80</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N97" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>18</v>
@@ -13840,7 +13832,7 @@
         <v>18</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13861,10 +13853,10 @@
         <v>18</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>18</v>
@@ -13875,13 +13867,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>18</v>
@@ -13903,19 +13895,19 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>18</v>
@@ -13964,7 +13956,7 @@
         <v>18</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13985,10 +13977,10 @@
         <v>18</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>18</v>
@@ -13999,10 +13991,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14025,13 +14017,13 @@
         <v>18</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14082,7 +14074,7 @@
         <v>18</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14106,7 +14098,7 @@
         <v>18</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>18</v>
@@ -14117,10 +14109,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14149,7 +14141,7 @@
         <v>137</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>139</v>
@@ -14202,7 +14194,7 @@
         <v>18</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14226,7 +14218,7 @@
         <v>18</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>18</v>
@@ -14237,14 +14229,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14266,10 +14258,10 @@
         <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>139</v>
@@ -14324,7 +14316,7 @@
         <v>18</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14359,10 +14351,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14388,16 +14380,16 @@
         <v>188</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N102" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O102" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>18</v>
@@ -14407,7 +14399,7 @@
         <v>18</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>18</v>
@@ -14422,14 +14414,14 @@
         <v>18</v>
       </c>
       <c r="X102" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y102" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y102" t="s" s="2">
+      <c r="Z102" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>18</v>
       </c>
@@ -14446,7 +14438,7 @@
         <v>18</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>90</v>
@@ -14464,16 +14456,16 @@
         <v>18</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>18</v>
@@ -14481,10 +14473,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14507,19 +14499,19 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M103" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O103" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>18</v>
@@ -14568,7 +14560,7 @@
         <v>18</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14586,27 +14578,27 @@
         <v>18</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM103" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP103" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14632,16 +14624,16 @@
         <v>188</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N104" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O104" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>18</v>
@@ -14666,14 +14658,14 @@
         <v>18</v>
       </c>
       <c r="X104" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y104" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y104" t="s" s="2">
+      <c r="Z104" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z104" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA104" t="s" s="2">
         <v>18</v>
       </c>
@@ -14690,7 +14682,7 @@
         <v>18</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14699,7 +14691,7 @@
         <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>102</v>
@@ -14714,7 +14706,7 @@
         <v>133</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>18</v>
@@ -14725,14 +14717,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14754,16 +14746,16 @@
         <v>188</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>18</v>
@@ -14788,14 +14780,14 @@
         <v>18</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z105" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA105" t="s" s="2">
         <v>18</v>
       </c>
@@ -14812,7 +14804,7 @@
         <v>18</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14830,27 +14822,27 @@
         <v>18</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM105" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AN105" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AO105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP105" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14876,16 +14868,16 @@
         <v>80</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M106" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N106" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O106" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>18</v>
@@ -14934,7 +14926,7 @@
         <v>18</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14955,10 +14947,10 @@
         <v>18</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>18</v>
@@ -14969,13 +14961,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C107" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>18</v>
@@ -14997,19 +14989,19 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>18</v>
@@ -15058,7 +15050,7 @@
         <v>18</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15079,10 +15071,10 @@
         <v>18</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>18</v>
@@ -15093,10 +15085,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15119,13 +15111,13 @@
         <v>18</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15176,7 +15168,7 @@
         <v>18</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15200,7 +15192,7 @@
         <v>18</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>18</v>
@@ -15211,10 +15203,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15243,7 +15235,7 @@
         <v>137</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>139</v>
@@ -15296,7 +15288,7 @@
         <v>18</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15320,7 +15312,7 @@
         <v>18</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>18</v>
@@ -15331,14 +15323,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15360,10 +15352,10 @@
         <v>136</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>139</v>
@@ -15418,7 +15410,7 @@
         <v>18</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15453,10 +15445,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15482,16 +15474,16 @@
         <v>188</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O111" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>18</v>
@@ -15501,7 +15493,7 @@
         <v>18</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>18</v>
@@ -15516,14 +15508,14 @@
         <v>18</v>
       </c>
       <c r="X111" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y111" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y111" t="s" s="2">
+      <c r="Z111" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z111" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA111" t="s" s="2">
         <v>18</v>
       </c>
@@ -15540,7 +15532,7 @@
         <v>18</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>90</v>
@@ -15558,16 +15550,16 @@
         <v>18</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM111" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN111" t="s" s="2">
+      <c r="AO111" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>18</v>
@@ -15575,10 +15567,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15601,19 +15593,19 @@
         <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M112" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O112" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>18</v>
@@ -15662,7 +15654,7 @@
         <v>18</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15680,27 +15672,27 @@
         <v>18</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AO112" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP112" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15726,16 +15718,16 @@
         <v>188</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N113" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O113" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>18</v>
@@ -15760,14 +15752,14 @@
         <v>18</v>
       </c>
       <c r="X113" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y113" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y113" t="s" s="2">
+      <c r="Z113" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z113" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA113" t="s" s="2">
         <v>18</v>
       </c>
@@ -15784,7 +15776,7 @@
         <v>18</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15793,7 +15785,7 @@
         <v>90</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>102</v>
@@ -15808,7 +15800,7 @@
         <v>133</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>18</v>
@@ -15819,14 +15811,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15848,16 +15840,16 @@
         <v>188</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>18</v>
@@ -15882,14 +15874,14 @@
         <v>18</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z114" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>18</v>
       </c>
@@ -15906,7 +15898,7 @@
         <v>18</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15924,27 +15916,27 @@
         <v>18</v>
       </c>
       <c r="AL114" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM114" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM114" t="s" s="2">
+      <c r="AN114" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN114" t="s" s="2">
+      <c r="AO114" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15970,16 +15962,16 @@
         <v>80</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M115" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N115" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O115" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>18</v>
@@ -16028,7 +16020,7 @@
         <v>18</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16049,10 +16041,10 @@
         <v>18</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>18</v>
@@ -16063,13 +16055,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C116" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>18</v>
@@ -16091,19 +16083,19 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>18</v>
@@ -16152,7 +16144,7 @@
         <v>18</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16173,10 +16165,10 @@
         <v>18</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>18</v>
@@ -16187,10 +16179,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16213,13 +16205,13 @@
         <v>18</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16270,7 +16262,7 @@
         <v>18</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16294,7 +16286,7 @@
         <v>18</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>18</v>
@@ -16305,10 +16297,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16337,7 +16329,7 @@
         <v>137</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>139</v>
@@ -16390,7 +16382,7 @@
         <v>18</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16414,7 +16406,7 @@
         <v>18</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>18</v>
@@ -16425,14 +16417,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16454,10 +16446,10 @@
         <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>139</v>
@@ -16512,7 +16504,7 @@
         <v>18</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16547,10 +16539,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16576,16 +16568,16 @@
         <v>188</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N120" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O120" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>18</v>
@@ -16595,7 +16587,7 @@
         <v>18</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>18</v>
@@ -16610,14 +16602,14 @@
         <v>18</v>
       </c>
       <c r="X120" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y120" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y120" t="s" s="2">
+      <c r="Z120" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z120" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA120" t="s" s="2">
         <v>18</v>
       </c>
@@ -16634,7 +16626,7 @@
         <v>18</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>90</v>
@@ -16652,16 +16644,16 @@
         <v>18</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN120" t="s" s="2">
+      <c r="AO120" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>18</v>
@@ -16669,10 +16661,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16695,19 +16687,19 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M121" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O121" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>18</v>
@@ -16756,7 +16748,7 @@
         <v>18</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16774,27 +16766,27 @@
         <v>18</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM121" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN121" t="s" s="2">
+      <c r="AO121" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP121" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16820,16 +16812,16 @@
         <v>188</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N122" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O122" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>18</v>
@@ -16854,14 +16846,14 @@
         <v>18</v>
       </c>
       <c r="X122" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y122" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y122" t="s" s="2">
+      <c r="Z122" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z122" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA122" t="s" s="2">
         <v>18</v>
       </c>
@@ -16878,7 +16870,7 @@
         <v>18</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16887,7 +16879,7 @@
         <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>102</v>
@@ -16902,7 +16894,7 @@
         <v>133</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>18</v>
@@ -16913,14 +16905,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16942,16 +16934,16 @@
         <v>188</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>18</v>
@@ -16976,14 +16968,14 @@
         <v>18</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y123" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z123" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z123" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA123" t="s" s="2">
         <v>18</v>
       </c>
@@ -17000,7 +16992,7 @@
         <v>18</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17018,27 +17010,27 @@
         <v>18</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM123" t="s" s="2">
+      <c r="AN123" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN123" t="s" s="2">
+      <c r="AO123" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP123" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17064,16 +17056,16 @@
         <v>80</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M124" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N124" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O124" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>18</v>
@@ -17122,7 +17114,7 @@
         <v>18</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17143,10 +17135,10 @@
         <v>18</v>
       </c>
       <c r="AM124" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-urinalysis.xlsx
+++ b/StructureDefinition-onc-urinalysis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
